--- a/docs/WiseTrader_Regression_Matrix.xlsx
+++ b/docs/WiseTrader_Regression_Matrix.xlsx
@@ -874,7 +874,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1" s="9">
+    <row r="5" ht="90" customHeight="1" s="9">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>XAGUSD</t>
@@ -882,23 +882,23 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>S5_silver_tuned (CONFIRMED = S1, reproducible)</t>
+          <t>S0_baseline (S5 REJECTED - failed OOS)</t>
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>11.01</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="E5" s="17" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>Strong secondary market, confirmed twice (S1/S5 identical). Next: model-4 confirm + widen window (n=37 is thin). Not yet a live candidate - needs its own OOS pass.</t>
+          <t>S5_silver_tuned (ADX gate on) looked strong in-sample on BOTH models (model1 PF1.57, model4 PF1.53) but collapsed OOS: PF 0.75, net -$552. REJECTED. XAGUSD reverts to S0_baseline = A2_tuned's toggles as-is (no XAGUSD-specific tuning needed beyond the profile_bin no-op) - same conclusion as the original 2026-07-17 gauntlet, before this whole tuning attempt.</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="9" min="1" max="1"/>
@@ -3179,6 +3179,150 @@
       <c r="N9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">  [2026.01.01-2026.07.08, 2026-07-22 20:11:26]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>S5_silver_tuned (model4 confirm)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Confirms model-1 result (PF 1.57-&gt;1.53, exp $11.01-&gt;$9.98) - not a fill artifact. Same window as tuning though (2026 primary) - still needs a genuine OOS window before fully trusting.</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>379.14</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>9.98</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>25 (65.79%)</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>43.91</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>-55.27</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>344.85 (3.41%)</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>380.75 (3.76%)</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>8.07</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>[2026.01.01-2026.07.08, 2026-07-23 15:43:14]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>S5_silver_tuned (OOS, REJECTED)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>REJECTED - OOS on the untouched 2025H2 window: PF collapses 1.53-&gt;0.75, net swings +$379 to -$552. Same overfit pattern as EURUSD's E9. ADX-gate-on for XAGUSD was in-sample noise, not real structure.</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>-551.95</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>-7.26</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>46 (60.53%)</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>35.61</t>
+        </is>
+      </c>
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>-73.00</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
+        <is>
+          <t>899.37 (8.69%)</t>
+        </is>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>946.92 (9.12%)</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>[2025.07.01-2025.12.31, 2026-07-23 21:28:54]</t>
         </is>
       </c>
     </row>
